--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ36"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127042640</v>
+        <v>136944401</v>
       </c>
       <c r="B9" t="n">
-        <v>78334</v>
+        <v>80095</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,34 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Holmängena, Holmängena, Hjd</t>
+          <t>Dödåsen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436612</v>
+        <v>436334</v>
       </c>
       <c r="R9" t="n">
-        <v>6852981</v>
+        <v>6852908</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,12 +1459,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1479,24 +1489,24 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127042640</t>
+          <t>https://artportalen.se/Sighting/136944401</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127045435</v>
+        <v>127042640</v>
       </c>
       <c r="B10" t="n">
         <v>78334</v>
@@ -1531,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436671</v>
+        <v>436612</v>
       </c>
       <c r="R10" t="n">
-        <v>6852588</v>
+        <v>6852981</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,13 +1602,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127045435</t>
+          <t>https://artportalen.se/Sighting/127042640</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127045862</v>
+        <v>127045435</v>
       </c>
       <c r="B11" t="n">
         <v>78334</v>
@@ -1633,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436614</v>
+        <v>436671</v>
       </c>
       <c r="R11" t="n">
-        <v>6852662</v>
+        <v>6852588</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,58 +1704,54 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127045862</t>
+          <t>https://artportalen.se/Sighting/127045435</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127042671</v>
+        <v>127045862</v>
       </c>
       <c r="B12" t="n">
-        <v>57141</v>
+        <v>78334</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436712</v>
+        <v>436614</v>
       </c>
       <c r="R12" t="n">
-        <v>6852917</v>
+        <v>6852662</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1800,13 +1806,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127042671</t>
+          <t>https://artportalen.se/Sighting/127045862</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127042782</v>
+        <v>127042671</v>
       </c>
       <c r="B13" t="n">
         <v>57141</v>
@@ -1834,20 +1840,24 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436839</v>
+        <v>436712</v>
       </c>
       <c r="R13" t="n">
-        <v>6852857</v>
+        <v>6852917</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1877,11 +1887,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1907,13 +1912,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127042782</t>
+          <t>https://artportalen.se/Sighting/127042671</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127043085</v>
+        <v>127042782</v>
       </c>
       <c r="B14" t="n">
         <v>57141</v>
@@ -1948,10 +1953,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436966</v>
+        <v>436839</v>
       </c>
       <c r="R14" t="n">
-        <v>6852719</v>
+        <v>6852857</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,60 +2019,51 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127043085</t>
+          <t>https://artportalen.se/Sighting/127042782</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127043665</v>
+        <v>127043085</v>
       </c>
       <c r="B15" t="n">
-        <v>58057</v>
+        <v>57141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436739</v>
+        <v>436966</v>
       </c>
       <c r="R15" t="n">
-        <v>6852982</v>
+        <v>6852719</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,6 +2098,11 @@
           <t>2025-07-31</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2125,16 +2126,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127043665</t>
+          <t>https://artportalen.se/Sighting/127043085</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127042693</v>
+        <v>136944402</v>
       </c>
       <c r="B16" t="n">
-        <v>79085</v>
+        <v>58169</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2142,37 +2143,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Holmängena, Holmängena, Hjd</t>
+          <t>Dödåsen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436690</v>
+        <v>436320</v>
       </c>
       <c r="R16" t="n">
-        <v>6852851</v>
+        <v>6852884</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2196,12 +2197,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2216,27 +2227,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127042693</t>
+          <t>https://artportalen.se/Sighting/136944402</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127042707</v>
+        <v>127043665</v>
       </c>
       <c r="B17" t="n">
-        <v>79085</v>
+        <v>58057</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2244,34 +2255,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436693</v>
+        <v>436739</v>
       </c>
       <c r="R17" t="n">
-        <v>6852823</v>
+        <v>6852982</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2329,13 +2349,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127042707</t>
+          <t>https://artportalen.se/Sighting/127043665</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127042718</v>
+        <v>127042693</v>
       </c>
       <c r="B18" t="n">
         <v>79085</v>
@@ -2370,10 +2390,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436698</v>
+        <v>436690</v>
       </c>
       <c r="R18" t="n">
-        <v>6852807</v>
+        <v>6852851</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2431,13 +2451,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127042718</t>
+          <t>https://artportalen.se/Sighting/127042693</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127042774</v>
+        <v>127042707</v>
       </c>
       <c r="B19" t="n">
         <v>79085</v>
@@ -2472,13 +2492,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436811</v>
+        <v>436693</v>
       </c>
       <c r="R19" t="n">
-        <v>6852876</v>
+        <v>6852823</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2533,13 +2553,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127042774</t>
+          <t>https://artportalen.se/Sighting/127042707</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127042878</v>
+        <v>127042718</v>
       </c>
       <c r="B20" t="n">
         <v>79085</v>
@@ -2574,13 +2594,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436744</v>
+        <v>436698</v>
       </c>
       <c r="R20" t="n">
-        <v>6852740</v>
+        <v>6852807</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2635,13 +2655,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127042878</t>
+          <t>https://artportalen.se/Sighting/127042718</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127042921</v>
+        <v>127042774</v>
       </c>
       <c r="B21" t="n">
         <v>79085</v>
@@ -2676,13 +2696,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436818</v>
+        <v>436811</v>
       </c>
       <c r="R21" t="n">
-        <v>6852702</v>
+        <v>6852876</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2737,13 +2757,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127042921</t>
+          <t>https://artportalen.se/Sighting/127042774</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127043023</v>
+        <v>127042878</v>
       </c>
       <c r="B22" t="n">
         <v>79085</v>
@@ -2778,10 +2798,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436949</v>
+        <v>436744</v>
       </c>
       <c r="R22" t="n">
-        <v>6852713</v>
+        <v>6852740</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2839,13 +2859,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127043023</t>
+          <t>https://artportalen.se/Sighting/127042878</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127043155</v>
+        <v>127042921</v>
       </c>
       <c r="B23" t="n">
         <v>79085</v>
@@ -2880,10 +2900,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437036</v>
+        <v>436818</v>
       </c>
       <c r="R23" t="n">
-        <v>6852766</v>
+        <v>6852702</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2941,13 +2961,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127043155</t>
+          <t>https://artportalen.se/Sighting/127042921</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127043256</v>
+        <v>127043023</v>
       </c>
       <c r="B24" t="n">
         <v>79085</v>
@@ -2982,10 +3002,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437153</v>
+        <v>436949</v>
       </c>
       <c r="R24" t="n">
-        <v>6852858</v>
+        <v>6852713</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3043,13 +3063,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127043256</t>
+          <t>https://artportalen.se/Sighting/127043023</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127044451</v>
+        <v>127043155</v>
       </c>
       <c r="B25" t="n">
         <v>79085</v>
@@ -3084,10 +3104,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436598</v>
+        <v>437036</v>
       </c>
       <c r="R25" t="n">
-        <v>6852836</v>
+        <v>6852766</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3145,13 +3165,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127044451</t>
+          <t>https://artportalen.se/Sighting/127043155</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127044529</v>
+        <v>127043256</v>
       </c>
       <c r="B26" t="n">
         <v>79085</v>
@@ -3186,10 +3206,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436642</v>
+        <v>437153</v>
       </c>
       <c r="R26" t="n">
-        <v>6852804</v>
+        <v>6852858</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3247,13 +3267,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127044529</t>
+          <t>https://artportalen.se/Sighting/127043256</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127044713</v>
+        <v>127044451</v>
       </c>
       <c r="B27" t="n">
         <v>79085</v>
@@ -3288,10 +3308,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436697</v>
+        <v>436598</v>
       </c>
       <c r="R27" t="n">
-        <v>6852687</v>
+        <v>6852836</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3349,13 +3369,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127044713</t>
+          <t>https://artportalen.se/Sighting/127044451</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127044760</v>
+        <v>127044529</v>
       </c>
       <c r="B28" t="n">
         <v>79085</v>
@@ -3390,10 +3410,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436777</v>
+        <v>436642</v>
       </c>
       <c r="R28" t="n">
-        <v>6852598</v>
+        <v>6852804</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3451,13 +3471,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127044760</t>
+          <t>https://artportalen.se/Sighting/127044529</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127045757</v>
+        <v>127044713</v>
       </c>
       <c r="B29" t="n">
         <v>79085</v>
@@ -3492,10 +3512,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436652</v>
+        <v>436697</v>
       </c>
       <c r="R29" t="n">
-        <v>6852648</v>
+        <v>6852687</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3553,16 +3573,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127045757</t>
+          <t>https://artportalen.se/Sighting/127044713</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127042769</v>
+        <v>127044760</v>
       </c>
       <c r="B30" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3570,21 +3590,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3594,13 +3614,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436811</v>
+        <v>436777</v>
       </c>
       <c r="R30" t="n">
-        <v>6852876</v>
+        <v>6852598</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3655,16 +3675,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127042769</t>
+          <t>https://artportalen.se/Sighting/127044760</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127042916</v>
+        <v>127045757</v>
       </c>
       <c r="B31" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3672,21 +3692,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3696,10 +3716,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436818</v>
+        <v>436652</v>
       </c>
       <c r="R31" t="n">
-        <v>6852702</v>
+        <v>6852648</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3757,13 +3777,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127042916</t>
+          <t>https://artportalen.se/Sighting/127045757</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127043039</v>
+        <v>127042769</v>
       </c>
       <c r="B32" t="n">
         <v>79917</v>
@@ -3798,13 +3818,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436949</v>
+        <v>436811</v>
       </c>
       <c r="R32" t="n">
-        <v>6852713</v>
+        <v>6852876</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3859,13 +3879,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127043039</t>
+          <t>https://artportalen.se/Sighting/127042769</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127043071</v>
+        <v>127042916</v>
       </c>
       <c r="B33" t="n">
         <v>79917</v>
@@ -3900,10 +3920,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436968</v>
+        <v>436818</v>
       </c>
       <c r="R33" t="n">
-        <v>6852714</v>
+        <v>6852702</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3961,13 +3981,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127043071</t>
+          <t>https://artportalen.se/Sighting/127042916</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127043219</v>
+        <v>127043039</v>
       </c>
       <c r="B34" t="n">
         <v>79917</v>
@@ -4002,10 +4022,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>437153</v>
+        <v>436949</v>
       </c>
       <c r="R34" t="n">
-        <v>6852858</v>
+        <v>6852713</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4063,13 +4083,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127043219</t>
+          <t>https://artportalen.se/Sighting/127043039</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127044642</v>
+        <v>127043071</v>
       </c>
       <c r="B35" t="n">
         <v>79917</v>
@@ -4104,10 +4124,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436684</v>
+        <v>436968</v>
       </c>
       <c r="R35" t="n">
-        <v>6852712</v>
+        <v>6852714</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4165,13 +4185,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127044642</t>
+          <t>https://artportalen.se/Sighting/127043071</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127045829</v>
+        <v>127043219</v>
       </c>
       <c r="B36" t="n">
         <v>79917</v>
@@ -4206,10 +4226,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436614</v>
+        <v>437153</v>
       </c>
       <c r="R36" t="n">
-        <v>6852662</v>
+        <v>6852858</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4266,6 +4286,210 @@
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127043219</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127044642</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Holmängena, Holmängena, Hjd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>436684</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6852712</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127044642</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127045829</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Holmängena, Holmängena, Hjd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>436614</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6852662</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/127045829</t>
         </is>
@@ -4308,6 +4532,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -1397,7 +1397,7 @@
         <v>136944401</v>
       </c>
       <c r="B9" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -1397,7 +1397,7 @@
         <v>136944401</v>
       </c>
       <c r="B9" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -1397,7 +1397,7 @@
         <v>136944401</v>
       </c>
       <c r="B9" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -1397,7 +1397,7 @@
         <v>136944401</v>
       </c>
       <c r="B9" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -1397,7 +1397,7 @@
         <v>136944401</v>
       </c>
       <c r="B9" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -1397,7 +1397,7 @@
         <v>136944401</v>
       </c>
       <c r="B9" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>136944402</v>
       </c>
       <c r="B16" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -1397,7 +1397,7 @@
         <v>136944401</v>
       </c>
       <c r="B9" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>136944402</v>
       </c>
       <c r="B16" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -1397,7 +1397,7 @@
         <v>136944401</v>
       </c>
       <c r="B9" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>136944402</v>
       </c>
       <c r="B16" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -1397,7 +1397,7 @@
         <v>136944401</v>
       </c>
       <c r="B9" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>136944402</v>
       </c>
       <c r="B16" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -1397,7 +1397,7 @@
         <v>136944401</v>
       </c>
       <c r="B9" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>136944402</v>
       </c>
       <c r="B16" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -1397,7 +1397,7 @@
         <v>136944401</v>
       </c>
       <c r="B9" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -1397,7 +1397,7 @@
         <v>136944401</v>
       </c>
       <c r="B9" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -1397,7 +1397,7 @@
         <v>136944401</v>
       </c>
       <c r="B9" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -1397,7 +1397,7 @@
         <v>136944401</v>
       </c>
       <c r="B9" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -1397,7 +1397,7 @@
         <v>136944401</v>
       </c>
       <c r="B9" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>136944402</v>
       </c>
       <c r="B16" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
